--- a/Decipher-PMO-Program-Workbook.xlsx
+++ b/Decipher-PMO-Program-Workbook.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">SIEM detections delayed if ZTNA log schema slips</t>
   </si>
   <si>
-    <t xml:space="preserve">TPM C</t>
+    <t xml:space="preserve">PM C</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-01</t>
@@ -2120,16 +2120,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2157,11 +2161,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2249,34 +2253,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -2422,203 +2426,203 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="76"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2639,232 +2643,232 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>4200</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>2310</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <f aca="false">IFERROR((E5-C5)/(D5-C5),0)</f>
         <v>0.55</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>2847</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>1880</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <f aca="false">IFERROR((E6-C6)/(D6-C6),0)</f>
         <v>0.660344221988058</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <f aca="false">IFERROR((E7-C7)/(D7-C7),0)</f>
         <v>0.6</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <f aca="false">IFERROR((E8-C8)/(D8-C8),0)</f>
         <v>0.5</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2885,124 +2889,124 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>334</v>
       </c>
     </row>
@@ -3023,187 +3027,187 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>2847</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>569</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>1367</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <f aca="false">IFERROR((D5-F5)/(D5-E5),0)</f>
         <v>0.649692712906058</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>320000</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>320000</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <f aca="false">IFERROR((D6-F6)/(D6-E6),0)</f>
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>127</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <f aca="false">IFERROR((D7-F7)/(D7-E7),0)</f>
         <v>0.789473684210526</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>200000</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>120000</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>118000</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <f aca="false">IFERROR((D8-F8)/(D8-E8),0)</f>
         <v>1.025</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3224,211 +3228,211 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <f aca="false">IF(OR(D5="",E5=""),"",D5*E5)</f>
         <v>16</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <f aca="false">IF(OR(D6="",E6=""),"",D6*E6)</f>
         <v>9</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="4" t="str">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="5" t="str">
         <f aca="false">IF(OR(D7="",E7=""),"",D7*E7)</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="5" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="4" t="str">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="5" t="str">
         <f aca="false">IF(OR(D8="",E8=""),"",D8*E8)</f>
         <v/>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="4" t="str">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="5" t="str">
         <f aca="false">IF(OR(D9="",E9=""),"",D9*E9)</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="5" t="s">
         <v>408</v>
       </c>
     </row>
@@ -3449,235 +3453,235 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <f aca="false">D5*E5</f>
         <v>16</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <f aca="false">I5*J5</f>
         <v>8</v>
       </c>
-      <c r="L5" s="4" t="str">
+      <c r="L5" s="5" t="str">
         <f aca="false">IF(K5&gt;=15,"High",IF(K5&gt;=8,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <f aca="false">D6*E6</f>
         <v>12</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <f aca="false">I6*J6</f>
         <v>6</v>
       </c>
-      <c r="L6" s="4" t="str">
+      <c r="L6" s="5" t="str">
         <f aca="false">IF(K6&gt;=15,"High",IF(K6&gt;=8,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <f aca="false">D7*E7</f>
         <v>9</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="5" t="n">
         <f aca="false">I7*J7</f>
         <v>4</v>
       </c>
-      <c r="L7" s="4" t="str">
+      <c r="L7" s="5" t="str">
         <f aca="false">IF(K7&gt;=15,"High",IF(K7&gt;=8,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="5" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="9" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="10" t="n">
         <f aca="false">SUM(K5:K7)</f>
         <v>18</v>
       </c>
@@ -3699,187 +3703,187 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="8" t="n">
         <v>-3</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>407</v>
       </c>
     </row>
@@ -3900,179 +3904,179 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>3.2</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>2.4</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <f aca="false">MAX(C5:F5)</f>
         <v>3.2</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <f aca="false">G5-B5</f>
         <v>1.2</v>
       </c>
-      <c r="I5" s="4" t="str">
+      <c r="I5" s="5" t="str">
         <f aca="false">IF(H5&gt;0,"SHORT","ok")</f>
         <v>SHORT</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>5.5</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <f aca="false">MAX(C6:F6)</f>
         <v>5.5</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <f aca="false">G6-B6</f>
         <v>-0.5</v>
       </c>
-      <c r="I6" s="4" t="str">
+      <c r="I6" s="5" t="str">
         <f aca="false">IF(H6&gt;0,"SHORT","ok")</f>
         <v>ok</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>1.8</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <f aca="false">MAX(C7:F7)</f>
         <v>1.8</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <f aca="false">G7-B7</f>
         <v>0.3</v>
       </c>
-      <c r="I7" s="4" t="str">
+      <c r="I7" s="5" t="str">
         <f aca="false">IF(H7&gt;0,"SHORT","ok")</f>
         <v>SHORT</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>3.5</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <f aca="false">MAX(C8:F8)</f>
         <v>3.5</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <f aca="false">G8-B8</f>
         <v>0.5</v>
       </c>
-      <c r="I8" s="4" t="str">
+      <c r="I8" s="5" t="str">
         <f aca="false">IF(H8&gt;0,"SHORT","ok")</f>
         <v>SHORT</v>
       </c>
@@ -4094,204 +4098,204 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="G5" s="4" t="str">
+      <c r="G5" s="5" t="str">
         <f aca="false">IF(E5=F5,"aligned","GAP")</f>
         <v>aligned</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="5" t="str">
         <f aca="false">IF(E6=F6,"aligned","GAP")</f>
         <v>GAP</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="5" t="str">
         <f aca="false">IF(E7=F7,"aligned","GAP")</f>
         <v>GAP</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="G8" s="4" t="str">
+      <c r="G8" s="5" t="str">
         <f aca="false">IF(E8=F8,"aligned","GAP")</f>
         <v>aligned</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="G9" s="4" t="str">
+      <c r="G9" s="5" t="str">
         <f aca="false">IF(E9=F9,"aligned","GAP")</f>
         <v>GAP</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>441</v>
       </c>
     </row>
@@ -4312,297 +4316,297 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>552</v>
       </c>
     </row>
@@ -4623,124 +4627,124 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>565</v>
       </c>
     </row>
@@ -4761,355 +4765,355 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5130,221 +5134,221 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>2400000</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>1900000</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>1080000</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>2460000</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <f aca="false">B5-E5</f>
         <v>-60000</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <f aca="false">IFERROR(D5/B5,0)</f>
         <v>0.45</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>900000</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>540000</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>360000</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>900000</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <f aca="false">B6-E6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <f aca="false">IFERROR(D6/B6,0)</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>1200000</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>1200000</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <f aca="false">B7-E7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <f aca="false">IFERROR(D7/B7,0)</f>
         <v>0.075</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>140000</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <f aca="false">B8-E8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <f aca="false">IFERROR(D8/B8,0)</f>
         <v>0.466666666666667</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <f aca="false">B9-E9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <f aca="false">IFERROR(D9/B9,0)</f>
         <v>0.277777777777778</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <f aca="false">B10-E10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <f aca="false">IFERROR(D10/B10,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <f aca="false">SUM(B5:B10)</f>
         <v>5100000</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <f aca="false">SUM(C5:C10)</f>
         <v>2790000</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <f aca="false">SUM(D5:D10)</f>
         <v>1720000</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <f aca="false">SUM(E5:E10)</f>
         <v>5160000</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <f aca="false">SUM(F5:F10)</f>
         <v>-60000</v>
       </c>
@@ -5366,170 +5370,170 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5550,124 +5554,124 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5688,134 +5692,134 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5836,170 +5840,170 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <f aca="false">COUNTIF(Components!D5:D7,"Red")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <f aca="false">COUNTIF(Components!D5:D7,"Amber")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <f aca="false">COUNTIF(Components!D5:D7,"Green")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <f aca="false">IFERROR(AVERAGE(Components!E5:E7),0)</f>
         <v>35</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <f aca="false">SUM(Financials!B5:B10)</f>
         <v>5100000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <f aca="false">SUM(Financials!D5:D10)</f>
         <v>1720000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <f aca="false">SUM(Financials!E5:E10)</f>
         <v>5160000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <f aca="false">SUM(Financials!B5:B10)-SUM(Financials!E5:E10)</f>
         <v>-60000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <f aca="false">COUNTIF(Benefits!J5:J8,"Green")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <f aca="false">IFERROR(AVERAGE(Benefits!G5:G8),0)</f>
         <v>0.866041599279146</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <f aca="false">IFERROR(AVERAGE('Program OKRs &amp; KPIs'!F5:F8),0)</f>
         <v>0.577586055497015</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <f aca="false">COUNTIF('Program Risk'!L5:L7,"High")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <f aca="false">SUM('Program Risk'!K5:K7)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <f aca="false">COUNTIF(Milestones!E5:E9,"Red")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <f aca="false">COUNTIF(Milestones!E5:E9,"Amber")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="5" t="n">
         <f aca="false">COUNTIF('Master Schedule'!I5:I12,"At risk")+COUNTIF('Master Schedule'!I5:I12,"Late")</f>
         <v>2</v>
       </c>
@@ -6021,134 +6025,134 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>6400000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="8" t="n">
         <v>300000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>1210000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>179</v>
       </c>
     </row>
@@ -6169,256 +6173,256 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G9" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>228</v>
       </c>
     </row>
@@ -6439,293 +6443,293 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <f aca="false">E5-D5</f>
         <v>6</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <f aca="false">E6-D6</f>
         <v>7</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <f aca="false">E7-D7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <f aca="false">E8-D8</f>
         <v>14</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <f aca="false">E9-D9</f>
         <v>9</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <f aca="false">E10-D10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <f aca="false">E11-D11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <f aca="false">E12-D12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>244</v>
       </c>
     </row>
@@ -6746,131 +6750,131 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <f aca="false">C5-B5</f>
         <v>7</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="5" t="str">
         <f aca="false">IF(D5&lt;=5,"Green",IF(D5&lt;=14,"Amber","Red"))</f>
         <v>Amber</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <f aca="false">C6-B6</f>
         <v>14</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="5" t="str">
         <f aca="false">IF(D6&lt;=5,"Green",IF(D6&lt;=14,"Amber","Red"))</f>
         <v>Amber</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <f aca="false">C7-B7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="5" t="str">
         <f aca="false">IF(D7&lt;=5,"Green",IF(D7&lt;=14,"Amber","Red"))</f>
         <v>Green</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <f aca="false">C8-B8</f>
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="str">
+      <c r="E8" s="5" t="str">
         <f aca="false">IF(D8&lt;=5,"Green",IF(D8&lt;=14,"Amber","Red"))</f>
         <v>Amber</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <f aca="false">C9-B9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="4" t="str">
+      <c r="E9" s="5" t="str">
         <f aca="false">IF(D9&lt;=5,"Green",IF(D9&lt;=14,"Amber","Red"))</f>
         <v>Green</v>
       </c>
@@ -6892,189 +6896,189 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <f aca="false">G5-F5</f>
         <v>14</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="8" t="n">
         <v>2400000</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="8" t="n">
         <v>1080000</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="8" t="n">
         <v>2460000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <f aca="false">G6-F6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="8" t="n">
         <v>900000</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="8" t="n">
         <v>360000</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="8" t="n">
         <v>900000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <f aca="false">G7-F7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="8" t="n">
         <v>1200000</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="8" t="n">
         <v>90000</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K7" s="8" t="n">
         <v>1200000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <f aca="false">IFERROR(AVERAGE(E5:E7),0)</f>
         <v>35</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="11" t="n">
         <f aca="false">SUM(I5:I7)</f>
         <v>4500000</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="J8" s="11" t="n">
         <f aca="false">SUM(J5:J7)</f>
         <v>1530000</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="11" t="n">
         <f aca="false">SUM(K5:K7)</f>
         <v>4560000</v>
       </c>
@@ -7096,123 +7100,123 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>317</v>
       </c>
     </row>
